--- a/data/trans_dic/P1417-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1417-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,37</t>
+          <t>0,2; 1,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,38</t>
+          <t>0,22; 1,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,4</t>
+          <t>0,72; 2,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,29</t>
+          <t>2,62; 5,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,36</t>
+          <t>1,69; 3,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,8</t>
+          <t>2,76; 4,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,92</t>
+          <t>2,44; 5,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,16</t>
+          <t>5,56; 8,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,19</t>
+          <t>1,17; 2,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,16</t>
+          <t>1,81; 3,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,63</t>
+          <t>1,93; 3,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,54</t>
+          <t>4,53; 6,53</t>
         </is>
       </c>
     </row>
@@ -804,34 +804,34 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,57</t>
+          <t>0,1; 0,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,77</t>
+          <t>0,19; 0,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,78</t>
+          <t>0,15; 0,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,18</t>
+          <t>0,55; 1,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,9</t>
+          <t>0,78; 1,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,97</t>
+          <t>1,51; 2,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,74</t>
+          <t>1,5; 2,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,45</t>
+          <t>3,2; 4,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,07</t>
+          <t>0,48; 1,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,66</t>
+          <t>0,88; 1,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,57</t>
+          <t>0,87; 1,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,6</t>
+          <t>1,94; 2,82</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,82</t>
+          <t>0,08; 0,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,73</t>
+          <t>0,46; 2,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,95</t>
+          <t>1,12; 4,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,5</t>
+          <t>0,92; 3,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,25</t>
+          <t>2,79; 5,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,89</t>
+          <t>0,38; 1,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,09</t>
+          <t>0,64; 2,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,99</t>
+          <t>0,46; 1,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,95</t>
+          <t>1,52; 2,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,67</t>
+          <t>0,22; 0,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,72</t>
+          <t>0,27; 0,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,88</t>
+          <t>0,35; 0,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,47</t>
+          <t>0,93; 1,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,2</t>
+          <t>1,29; 2,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,3</t>
+          <t>2,24; 3,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,04</t>
+          <t>1,96; 3,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,88</t>
+          <t>3,94; 5,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,35</t>
+          <t>0,81; 1,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,94</t>
+          <t>1,32; 1,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,84</t>
+          <t>1,23; 1,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,12</t>
+          <t>2,6; 3,33</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19543</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70075</t>
+          <t>76893</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2446; 14173</t>
+          <t>2083; 13043</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2182; 13466</t>
+          <t>2122; 12557</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5401; 18131</t>
+          <t>5456; 17698</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13392; 27125</t>
+          <t>15073; 30478</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21509; 44176</t>
+          <t>22271; 44133</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36039; 64227</t>
+          <t>36988; 65080</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25859; 48899</t>
+          <t>24242; 49795</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40888; 61305</t>
+          <t>45535; 66919</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27531; 51417</t>
+          <t>27382; 51157</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42119; 72971</t>
+          <t>41813; 74234</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35308; 63523</t>
+          <t>33817; 60784</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57694; 82634</t>
+          <t>63273; 91102</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>76230</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93389</t>
+          <t>103977</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1691; 9734</t>
+          <t>1708; 9833</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3949; 15208</t>
+          <t>3647; 14955</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3524; 16244</t>
+          <t>3159; 15311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10255; 26980</t>
+          <t>12298; 28955</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12602; 30223</t>
+          <t>12320; 29964</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26488; 52075</t>
+          <t>26403; 51827</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29354; 54442</t>
+          <t>29884; 54162</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55823; 99528</t>
+          <t>69332; 102937</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16291; 35128</t>
+          <t>15898; 35869</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33047; 61754</t>
+          <t>32892; 59792</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35031; 63827</t>
+          <t>35362; 63147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>72412; 117645</t>
+          <t>85236; 124134</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>28461</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>30509</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 10577</t>
+          <t>0; 10973</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6078</t>
+          <t>0; 5170</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5321</t>
+          <t>0; 5088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>563; 5314</t>
+          <t>580; 5596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2159; 13029</t>
+          <t>2180; 12908</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5078; 18098</t>
+          <t>5133; 18411</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4980; 19194</t>
+          <t>5073; 19466</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19067; 34674</t>
+          <t>20516; 38662</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4048; 19384</t>
+          <t>3919; 17997</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6055; 19601</t>
+          <t>6029; 19523</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6177; 21774</t>
+          <t>5084; 20279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20717; 38562</t>
+          <t>21947; 41368</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>42895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>153074</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>191676</t>
+          <t>211378</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7344; 22078</t>
+          <t>7324; 22343</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9163; 24518</t>
+          <t>9066; 24120</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11853; 29736</t>
+          <t>11962; 29915</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26970; 50501</t>
+          <t>32641; 55913</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43609; 74177</t>
+          <t>43731; 75000</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77324; 117272</t>
+          <t>79458; 119148</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67960; 107551</t>
+          <t>69394; 106898</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>124417; 177907</t>
+          <t>146827; 189557</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54087; 89947</t>
+          <t>54059; 89366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91830; 134877</t>
+          <t>91978; 133871</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87031; 127225</t>
+          <t>84949; 126825</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>160076; 221616</t>
+          <t>188054; 240887</t>
         </is>
       </c>
     </row>
